--- a/SQL Tables.xlsx
+++ b/SQL Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Documents\ANU\2026\Semester 2\CSC429 Computer Project I\Project\Athi Soko Connect Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5350454C-0AE4-491B-B076-365B30B06705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9133A32-FB04-4468-A8AF-713706CCADE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{374249BB-2482-4216-9575-E17B4A444083}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="80">
   <si>
     <t>table_name</t>
   </si>
@@ -208,6 +208,72 @@
   </si>
   <si>
     <t>is_nullable</t>
+  </si>
+  <si>
+    <t>is_computed</t>
+  </si>
+  <si>
+    <t>is_primary_key</t>
+  </si>
+  <si>
+    <t>is_foreign_key</t>
+  </si>
+  <si>
+    <t>fk_references</t>
+  </si>
+  <si>
+    <t>default_value</t>
+  </si>
+  <si>
+    <t>collation</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>SQL_Latin1_General_CP1_CI_AS</t>
+  </si>
+  <si>
+    <t>((0))</t>
+  </si>
+  <si>
+    <t>(sysutcdatetime())</t>
+  </si>
+  <si>
+    <t>Providers.id</t>
+  </si>
+  <si>
+    <t>('requested')</t>
+  </si>
+  <si>
+    <t>cancellation_reason</t>
+  </si>
+  <si>
+    <t>Categories.id</t>
+  </si>
+  <si>
+    <t>('per visit')</t>
+  </si>
+  <si>
+    <t>Residents.id, Residents.id</t>
+  </si>
+  <si>
+    <t>is_available</t>
+  </si>
+  <si>
+    <t>((1))</t>
+  </si>
+  <si>
+    <t>('open')</t>
+  </si>
+  <si>
+    <t>Courts.id</t>
+  </si>
+  <si>
+    <t>booking_id</t>
+  </si>
+  <si>
+    <t>('pending')</t>
   </si>
 </sst>
 </file>
@@ -568,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E192F9CA-0607-4644-86F3-9F2CC1EBCCC1}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -580,9 +646,13 @@
     <col min="7" max="7" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.90625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,8 +680,26 @@
       <c r="I1" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -639,8 +727,26 @@
       <c r="I2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -668,8 +774,26 @@
       <c r="I3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -697,8 +821,26 @@
       <c r="I4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -726,8 +868,26 @@
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -755,8 +915,26 @@
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -784,8 +962,26 @@
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" t="s">
+        <v>67</v>
+      </c>
+      <c r="O7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -813,8 +1009,26 @@
       <c r="I8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -842,8 +1056,26 @@
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -871,8 +1103,26 @@
       <c r="I10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -900,8 +1150,26 @@
       <c r="I11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -929,8 +1197,26 @@
       <c r="I12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" t="s">
+        <v>64</v>
+      </c>
+      <c r="O12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -958,8 +1244,26 @@
       <c r="I13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>64</v>
+      </c>
+      <c r="N13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -987,8 +1291,26 @@
       <c r="I14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1016,8 +1338,26 @@
       <c r="I15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1045,8 +1385,26 @@
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1074,8 +1432,26 @@
       <c r="I17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1103,86 +1479,140 @@
       <c r="I18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>64</v>
+      </c>
+      <c r="N18" t="s">
+        <v>66</v>
+      </c>
+      <c r="O18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>510</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>64</v>
+      </c>
+      <c r="N19" t="s">
+        <v>64</v>
+      </c>
+      <c r="O19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
         <v>2</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" t="s">
+        <v>64</v>
+      </c>
+      <c r="O20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
         <v>24</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>5</v>
       </c>
-      <c r="F20">
+      <c r="F21">
         <v>160</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
       <c r="G21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1190,28 +1620,46 @@
       <c r="I21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" t="s">
+        <v>64</v>
+      </c>
+      <c r="O21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
         <v>2</v>
       </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1219,28 +1667,46 @@
       <c r="I22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22" t="s">
+        <v>64</v>
+      </c>
+      <c r="O22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1248,86 +1714,140 @@
       <c r="I23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>64</v>
+      </c>
+      <c r="N23" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
+        <v>64</v>
+      </c>
+      <c r="N24" t="s">
+        <v>64</v>
+      </c>
+      <c r="O24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
         <v>4</v>
       </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F24">
+      <c r="F25">
         <v>8</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>27</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>7</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
+        <v>64</v>
+      </c>
+      <c r="N25" t="s">
+        <v>67</v>
+      </c>
+      <c r="O25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>2</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26" t="s">
-        <v>26</v>
-      </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1335,28 +1855,46 @@
       <c r="I26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>64</v>
+      </c>
+      <c r="N26" t="s">
+        <v>64</v>
+      </c>
+      <c r="O26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1364,28 +1902,46 @@
       <c r="I27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>64</v>
+      </c>
+      <c r="N27" t="s">
+        <v>64</v>
+      </c>
+      <c r="O27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1393,25 +1949,43 @@
       <c r="I28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>71</v>
+      </c>
+      <c r="N28" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
       </c>
       <c r="F29">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1420,85 +1994,139 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="s">
+        <v>64</v>
+      </c>
+      <c r="N29" t="s">
+        <v>64</v>
+      </c>
+      <c r="O29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>64</v>
+      </c>
+      <c r="N30" t="s">
+        <v>64</v>
+      </c>
+      <c r="O30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="F31">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>64</v>
+      </c>
+      <c r="N31" t="s">
+        <v>66</v>
+      </c>
+      <c r="O31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>29</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1507,21 +2135,39 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>64</v>
+      </c>
+      <c r="N32" t="s">
+        <v>72</v>
+      </c>
+      <c r="O32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>29</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
@@ -1538,86 +2184,140 @@
       <c r="I33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>64</v>
+      </c>
+      <c r="N33" t="s">
+        <v>64</v>
+      </c>
+      <c r="O33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>29</v>
       </c>
       <c r="B34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N34" t="s">
+        <v>64</v>
+      </c>
+      <c r="O34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>29</v>
       </c>
       <c r="B35">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
         <v>3</v>
       </c>
-      <c r="F35">
-        <v>4</v>
-      </c>
-      <c r="G35">
-        <v>10</v>
-      </c>
       <c r="H35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>64</v>
+      </c>
+      <c r="N35" t="s">
+        <v>64</v>
+      </c>
+      <c r="O35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>29</v>
       </c>
       <c r="B36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1625,144 +2325,234 @@
       <c r="I36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
+        <v>64</v>
+      </c>
+      <c r="N36" t="s">
+        <v>66</v>
+      </c>
+      <c r="O36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>29</v>
       </c>
       <c r="B37">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="s">
+        <v>64</v>
+      </c>
+      <c r="N37" t="s">
+        <v>66</v>
+      </c>
+      <c r="O37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>29</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="s">
+        <v>64</v>
+      </c>
+      <c r="N38" t="s">
+        <v>67</v>
+      </c>
+      <c r="O38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>29</v>
       </c>
       <c r="B39">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>73</v>
+      </c>
+      <c r="N39" t="s">
+        <v>64</v>
+      </c>
+      <c r="O39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40">
         <v>16</v>
       </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40" t="s">
         <v>7</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E40" t="s">
         <v>5</v>
       </c>
-      <c r="F39">
+      <c r="F40">
         <v>510</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" t="s">
-        <v>3</v>
-      </c>
-      <c r="F40">
-        <v>4</v>
-      </c>
       <c r="G40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="s">
+        <v>64</v>
+      </c>
+      <c r="N40" t="s">
+        <v>64</v>
+      </c>
+      <c r="O40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -1770,28 +2560,46 @@
       <c r="I41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>64</v>
+      </c>
+      <c r="N41" t="s">
+        <v>75</v>
+      </c>
+      <c r="O41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>42</v>
       </c>
       <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
         <v>3</v>
       </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42" t="s">
-        <v>43</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
       <c r="F42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -1799,28 +2607,46 @@
       <c r="I42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
+        <v>64</v>
+      </c>
+      <c r="N42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
       <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43">
         <v>4</v>
       </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43">
-        <v>40</v>
-      </c>
       <c r="G43">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -1828,54 +2654,90 @@
       <c r="I43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>68</v>
+      </c>
+      <c r="N43" t="s">
+        <v>64</v>
+      </c>
+      <c r="O43" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>42</v>
       </c>
       <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" t="s">
         <v>5</v>
       </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
-        <v>11</v>
-      </c>
       <c r="F44">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="G44">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" t="s">
+        <v>64</v>
+      </c>
+      <c r="O44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>42</v>
       </c>
       <c r="B45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E45" t="s">
         <v>5</v>
       </c>
       <c r="F45">
-        <v>-1</v>
+        <v>40</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -1884,56 +2746,92 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>64</v>
+      </c>
+      <c r="N45" t="s">
+        <v>76</v>
+      </c>
+      <c r="O45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G46">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>64</v>
+      </c>
+      <c r="N46" t="s">
+        <v>67</v>
+      </c>
+      <c r="O46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
         <v>5</v>
       </c>
       <c r="F47">
-        <v>300</v>
+        <v>-1</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -1942,30 +2840,48 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>64</v>
+      </c>
+      <c r="N47" t="s">
+        <v>64</v>
+      </c>
+      <c r="O47" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>45</v>
       </c>
       <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
         <v>3</v>
       </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48" t="s">
-        <v>31</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
       <c r="F48">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -1973,19 +2889,37 @@
       <c r="I48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" t="s">
+        <v>64</v>
+      </c>
+      <c r="O48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>45</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E49" t="s">
         <v>5</v>
@@ -2000,30 +2934,48 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="s">
+        <v>64</v>
+      </c>
+      <c r="N49" t="s">
+        <v>64</v>
+      </c>
+      <c r="O49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>45</v>
       </c>
       <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
         <v>5</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50" t="s">
-        <v>46</v>
-      </c>
-      <c r="E50" t="s">
-        <v>3</v>
-      </c>
       <c r="F50">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -2031,231 +2983,375 @@
       <c r="I50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="s">
+        <v>64</v>
+      </c>
+      <c r="N50" t="s">
+        <v>64</v>
+      </c>
+      <c r="O50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>45</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>64</v>
+      </c>
+      <c r="N51" t="s">
+        <v>64</v>
+      </c>
+      <c r="O51" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>45</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>4</v>
+      </c>
+      <c r="G52">
         <v>10</v>
       </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52">
-        <v>8</v>
-      </c>
-      <c r="G52">
-        <v>27</v>
-      </c>
       <c r="H52">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52" t="s">
+        <v>77</v>
+      </c>
+      <c r="N52" t="s">
+        <v>64</v>
+      </c>
+      <c r="O52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>45</v>
       </c>
       <c r="B53">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F53">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
       <c r="I53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
+        <v>64</v>
+      </c>
+      <c r="N53" t="s">
+        <v>66</v>
+      </c>
+      <c r="O53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>45</v>
       </c>
       <c r="B54">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54">
         <v>8</v>
       </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
       <c r="G54">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="s">
+        <v>64</v>
+      </c>
+      <c r="N54" t="s">
+        <v>67</v>
+      </c>
+      <c r="O54" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>45</v>
       </c>
       <c r="B55">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55">
+        <v>510</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="s">
+        <v>64</v>
+      </c>
+      <c r="N55" t="s">
+        <v>64</v>
+      </c>
+      <c r="O55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>64</v>
+      </c>
+      <c r="N56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O56" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57">
         <v>10</v>
       </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57" t="s">
         <v>12</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E57" t="s">
         <v>11</v>
       </c>
-      <c r="F55">
+      <c r="F57">
         <v>8</v>
       </c>
-      <c r="G55">
+      <c r="G57">
         <v>27</v>
       </c>
-      <c r="H55">
+      <c r="H57">
         <v>7</v>
       </c>
-      <c r="I55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="s">
-        <v>2</v>
-      </c>
-      <c r="E56" t="s">
-        <v>3</v>
-      </c>
-      <c r="F56">
-        <v>4</v>
-      </c>
-      <c r="G56">
-        <v>10</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57">
-        <v>4</v>
-      </c>
-      <c r="G57">
-        <v>10</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
       <c r="I57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="s">
+        <v>64</v>
+      </c>
+      <c r="N57" t="s">
+        <v>64</v>
+      </c>
+      <c r="O57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>47</v>
       </c>
       <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" t="s">
         <v>3</v>
       </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
       <c r="F58">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2263,19 +3359,37 @@
       <c r="I58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="s">
+        <v>64</v>
+      </c>
+      <c r="N58" t="s">
+        <v>64</v>
+      </c>
+      <c r="O58" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>47</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E59" t="s">
         <v>3</v>
@@ -2292,25 +3406,43 @@
       <c r="I59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59" t="s">
+        <v>68</v>
+      </c>
+      <c r="N59" t="s">
+        <v>64</v>
+      </c>
+      <c r="O59" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>47</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E60" t="s">
         <v>5</v>
       </c>
       <c r="F60">
-        <v>-1</v>
+        <v>300</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2319,36 +3451,260 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>64</v>
+      </c>
+      <c r="N60" t="s">
+        <v>64</v>
+      </c>
+      <c r="O60" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>47</v>
       </c>
       <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61">
+        <v>4</v>
+      </c>
+      <c r="G61">
+        <v>10</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="s">
+        <v>64</v>
+      </c>
+      <c r="N61" t="s">
+        <v>64</v>
+      </c>
+      <c r="O61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>47</v>
+      </c>
+      <c r="B62">
+        <v>5</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>49</v>
+      </c>
+      <c r="E62" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62">
+        <v>-1</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>64</v>
+      </c>
+      <c r="N62" t="s">
+        <v>64</v>
+      </c>
+      <c r="O62" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63">
         <v>6</v>
       </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63" t="s">
         <v>10</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E63" t="s">
         <v>11</v>
       </c>
-      <c r="F61">
+      <c r="F63">
         <v>8</v>
       </c>
-      <c r="G61">
+      <c r="G63">
         <v>27</v>
       </c>
-      <c r="H61">
+      <c r="H63">
         <v>7</v>
       </c>
-      <c r="I61">
-        <v>0</v>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="s">
+        <v>64</v>
+      </c>
+      <c r="N63" t="s">
+        <v>67</v>
+      </c>
+      <c r="O63" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>47</v>
+      </c>
+      <c r="B64">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>10</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="s">
+        <v>64</v>
+      </c>
+      <c r="N64" t="s">
+        <v>64</v>
+      </c>
+      <c r="O64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65">
+        <v>40</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="s">
+        <v>64</v>
+      </c>
+      <c r="N65" t="s">
+        <v>79</v>
+      </c>
+      <c r="O65" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
